--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/10.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/10.xlsx
@@ -426,13 +426,13 @@
         <v>0.2041673282844568</v>
       </c>
       <c r="E2">
-        <v>-10.85803377283222</v>
+        <v>-15.35525974490763</v>
       </c>
       <c r="F2">
-        <v>-4.132785590634645</v>
+        <v>-5.216912257415902</v>
       </c>
       <c r="G2">
-        <v>-9.1762132157408</v>
+        <v>-12.35243203156627</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.7125291072180772</v>
       </c>
       <c r="E3">
-        <v>-11.15889655441412</v>
+        <v>-15.98281412930055</v>
       </c>
       <c r="F3">
-        <v>-3.288610452687517</v>
+        <v>-5.325433357387054</v>
       </c>
       <c r="G3">
-        <v>-9.339914733837377</v>
+        <v>-12.00411040433682</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.621007088633984</v>
       </c>
       <c r="E4">
-        <v>-11.11716924023357</v>
+        <v>-17.22060400686185</v>
       </c>
       <c r="F4">
-        <v>-3.392688189910053</v>
+        <v>-5.061473256117588</v>
       </c>
       <c r="G4">
-        <v>-9.419043791649429</v>
+        <v>-11.89458966873962</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.377261426701633</v>
       </c>
       <c r="E5">
-        <v>-11.32560645699274</v>
+        <v>-17.45148517762039</v>
       </c>
       <c r="F5">
-        <v>-3.260976116130125</v>
+        <v>-5.25860978737062</v>
       </c>
       <c r="G5">
-        <v>-9.944146767376932</v>
+        <v>-12.68971673603679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.965268360632908</v>
       </c>
       <c r="E6">
-        <v>-13.23036054120825</v>
+        <v>-16.97462175972623</v>
       </c>
       <c r="F6">
-        <v>-3.331900104790416</v>
+        <v>-4.97645956630308</v>
       </c>
       <c r="G6">
-        <v>-10.00594570259317</v>
+        <v>-12.57114846505908</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.338417623313532</v>
       </c>
       <c r="E7">
-        <v>-13.43756840741527</v>
+        <v>-18.30298486985939</v>
       </c>
       <c r="F7">
-        <v>-3.697239950651499</v>
+        <v>-4.960819161370823</v>
       </c>
       <c r="G7">
-        <v>-10.2010087900905</v>
+        <v>-11.97537524399473</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.484138257674166</v>
       </c>
       <c r="E8">
-        <v>-13.98474984625011</v>
+        <v>-18.16267277846138</v>
       </c>
       <c r="F8">
-        <v>-3.427558315730898</v>
+        <v>-4.999542023982089</v>
       </c>
       <c r="G8">
-        <v>-9.355365120327585</v>
+        <v>-12.67507959648671</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.39155110270439</v>
       </c>
       <c r="E9">
-        <v>-13.95971013517272</v>
+        <v>-19.35336523959912</v>
       </c>
       <c r="F9">
-        <v>-3.534822782352003</v>
+        <v>-4.785782644057079</v>
       </c>
       <c r="G9">
-        <v>-9.572624758338556</v>
+        <v>-12.29385083905857</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.076686380289594</v>
       </c>
       <c r="E10">
-        <v>-15.31991176332201</v>
+        <v>-20.21096184606297</v>
       </c>
       <c r="F10">
-        <v>-3.230486397135284</v>
+        <v>-4.84926209486841</v>
       </c>
       <c r="G10">
-        <v>-9.680575131064202</v>
+        <v>-11.69569661892713</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.566970420634486</v>
       </c>
       <c r="E11">
-        <v>-16.66200539009506</v>
+        <v>-20.75394023503708</v>
       </c>
       <c r="F11">
-        <v>-3.18541409838156</v>
+        <v>-4.66439368485084</v>
       </c>
       <c r="G11">
-        <v>-8.390513547162143</v>
+        <v>-11.49682706581596</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.912255133696044</v>
       </c>
       <c r="E12">
-        <v>-16.24541337494681</v>
+        <v>-20.70696741495327</v>
       </c>
       <c r="F12">
-        <v>-2.889957811722852</v>
+        <v>-4.827960627105422</v>
       </c>
       <c r="G12">
-        <v>-7.973601132662672</v>
+        <v>-10.55735062470385</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.171187397288546</v>
       </c>
       <c r="E13">
-        <v>-16.99800433948501</v>
+        <v>-21.73903212275051</v>
       </c>
       <c r="F13">
-        <v>-3.052669878817745</v>
+        <v>-4.52873361202917</v>
       </c>
       <c r="G13">
-        <v>-7.673481682818949</v>
+        <v>-10.05363617403904</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.4118963085329068</v>
       </c>
       <c r="E14">
-        <v>-17.22317484467192</v>
+        <v>-22.68594769196612</v>
       </c>
       <c r="F14">
-        <v>-3.40552042934682</v>
+        <v>-4.524144456617661</v>
       </c>
       <c r="G14">
-        <v>-6.577168676512589</v>
+        <v>-9.093799841233128</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.2989678166768578</v>
       </c>
       <c r="E15">
-        <v>-17.55705980949753</v>
+        <v>-23.02165591656334</v>
       </c>
       <c r="F15">
-        <v>-2.388358983407876</v>
+        <v>-4.428364475668968</v>
       </c>
       <c r="G15">
-        <v>-6.690592475273506</v>
+        <v>-8.409363123109982</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.9001078778203923</v>
       </c>
       <c r="E16">
-        <v>-18.71299819826911</v>
+        <v>-24.22743699444418</v>
       </c>
       <c r="F16">
-        <v>-2.034021513390776</v>
+        <v>-4.268441521619301</v>
       </c>
       <c r="G16">
-        <v>-4.906655031698251</v>
+        <v>-8.549252039791014</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.344782342737328</v>
       </c>
       <c r="E17">
-        <v>-19.63422615544065</v>
+        <v>-24.76952244298345</v>
       </c>
       <c r="F17">
-        <v>-2.191515694215435</v>
+        <v>-4.023113059973602</v>
       </c>
       <c r="G17">
-        <v>-6.431269825782814</v>
+        <v>-7.76512926094539</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.60200448434669</v>
       </c>
       <c r="E18">
-        <v>-20.80622916561667</v>
+        <v>-25.47877464734707</v>
       </c>
       <c r="F18">
-        <v>-1.751921822734807</v>
+        <v>-3.414674717515157</v>
       </c>
       <c r="G18">
-        <v>-5.336080745022929</v>
+        <v>-7.842971221674023</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.660704533128269</v>
       </c>
       <c r="E19">
-        <v>-20.93958462804559</v>
+        <v>-26.48046276751452</v>
       </c>
       <c r="F19">
-        <v>-1.488376733534145</v>
+        <v>-3.32007101827844</v>
       </c>
       <c r="G19">
-        <v>-4.674578112760418</v>
+        <v>-7.305670847216841</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.528941458747381</v>
       </c>
       <c r="E20">
-        <v>-23.05134722432454</v>
+        <v>-26.69966510802765</v>
       </c>
       <c r="F20">
-        <v>-1.23147680763874</v>
+        <v>-3.357970483691322</v>
       </c>
       <c r="G20">
-        <v>-4.627958046596908</v>
+        <v>-7.586338944484474</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.228782032094449</v>
       </c>
       <c r="E21">
-        <v>-22.72202248553358</v>
+        <v>-28.39877293349427</v>
       </c>
       <c r="F21">
-        <v>-1.260037258952461</v>
+        <v>-2.642259390937744</v>
       </c>
       <c r="G21">
-        <v>-4.943902524779665</v>
+        <v>-6.949165841066548</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.7953589725505786</v>
       </c>
       <c r="E22">
-        <v>-22.80174337691367</v>
+        <v>-27.93818179757079</v>
       </c>
       <c r="F22">
-        <v>-1.015369006126793</v>
+        <v>-2.554324877660965</v>
       </c>
       <c r="G22">
-        <v>-5.124150942094717</v>
+        <v>-7.347223458128999</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.2675676815426021</v>
       </c>
       <c r="E23">
-        <v>-23.76287538849416</v>
+        <v>-29.40638768622225</v>
       </c>
       <c r="F23">
-        <v>-0.6441858566063628</v>
+        <v>-2.317967634987585</v>
       </c>
       <c r="G23">
-        <v>-5.276581875791457</v>
+        <v>-7.332864362877877</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.3122570861616009</v>
       </c>
       <c r="E24">
-        <v>-24.07673772152278</v>
+        <v>-28.72558913264503</v>
       </c>
       <c r="F24">
-        <v>-0.4794724538663064</v>
+        <v>-2.138583017176547</v>
       </c>
       <c r="G24">
-        <v>-4.446952513350433</v>
+        <v>-7.29371102624495</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.9050447319655256</v>
       </c>
       <c r="E25">
-        <v>-24.55925781324136</v>
+        <v>-29.08525308016386</v>
       </c>
       <c r="F25">
-        <v>-0.03260054638468229</v>
+        <v>-1.942247517202022</v>
       </c>
       <c r="G25">
-        <v>-4.802567255595156</v>
+        <v>-7.737109444621266</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.471397354283771</v>
       </c>
       <c r="E26">
-        <v>-23.8624777024862</v>
+        <v>-29.809880472852</v>
       </c>
       <c r="F26">
-        <v>-0.2010283485588918</v>
+        <v>-2.124998620138038</v>
       </c>
       <c r="G26">
-        <v>-5.583122451957023</v>
+        <v>-7.68438937372062</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.980573990305224</v>
       </c>
       <c r="E27">
-        <v>-24.46624664562182</v>
+        <v>-29.99286265740129</v>
       </c>
       <c r="F27">
-        <v>-0.2067275162901524</v>
+        <v>-1.989461974059385</v>
       </c>
       <c r="G27">
-        <v>-5.577853969372157</v>
+        <v>-8.129752377401749</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.40427184304762</v>
       </c>
       <c r="E28">
-        <v>-24.19136635408805</v>
+        <v>-28.91569822782774</v>
       </c>
       <c r="F28">
-        <v>-0.2263275174077915</v>
+        <v>-2.17459463327845</v>
       </c>
       <c r="G28">
-        <v>-5.147310857362482</v>
+        <v>-7.696624628246873</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.72415902184006</v>
       </c>
       <c r="E29">
-        <v>-23.3369137285971</v>
+        <v>-28.77479845702727</v>
       </c>
       <c r="F29">
-        <v>-0.6150165552515839</v>
+        <v>-2.237752677537495</v>
       </c>
       <c r="G29">
-        <v>-5.919999880271327</v>
+        <v>-8.071102000162389</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.928017231720121</v>
       </c>
       <c r="E30">
-        <v>-23.71167044607035</v>
+        <v>-29.55305834415857</v>
       </c>
       <c r="F30">
-        <v>-0.616949964769718</v>
+        <v>-2.00743920343494</v>
       </c>
       <c r="G30">
-        <v>-6.0354339523674</v>
+        <v>-8.138985275648221</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.011823985157863</v>
       </c>
       <c r="E31">
-        <v>-24.28978500285251</v>
+        <v>-29.32824916835693</v>
       </c>
       <c r="F31">
-        <v>-0.9693548536360864</v>
+        <v>-2.18109566065562</v>
       </c>
       <c r="G31">
-        <v>-5.76485899368901</v>
+        <v>-7.838294072739044</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.979722909929967</v>
       </c>
       <c r="E32">
-        <v>-23.46241131519944</v>
+        <v>-28.57401145552843</v>
       </c>
       <c r="F32">
-        <v>-0.5433139012326615</v>
+        <v>-2.341972893953312</v>
       </c>
       <c r="G32">
-        <v>-5.366699557587506</v>
+        <v>-8.034076420371221</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.840700030540014</v>
       </c>
       <c r="E33">
-        <v>-23.26304471197369</v>
+        <v>-28.09704213074548</v>
       </c>
       <c r="F33">
-        <v>-0.6638894036493519</v>
+        <v>-2.276896350789383</v>
       </c>
       <c r="G33">
-        <v>-5.439643761463211</v>
+        <v>-7.400696728844182</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.609710767586197</v>
       </c>
       <c r="E34">
-        <v>-23.1254280547255</v>
+        <v>-28.54369301285718</v>
       </c>
       <c r="F34">
-        <v>-0.8845598528159179</v>
+        <v>-2.715340448314925</v>
       </c>
       <c r="G34">
-        <v>-4.804535757016855</v>
+        <v>-7.428913656384935</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.305198884491507</v>
       </c>
       <c r="E35">
-        <v>-23.48747179233346</v>
+        <v>-28.11524980919353</v>
       </c>
       <c r="F35">
-        <v>-0.3757045260524179</v>
+        <v>-2.424316755628597</v>
       </c>
       <c r="G35">
-        <v>-4.768927811538661</v>
+        <v>-6.797400647240542</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.947675896489574</v>
       </c>
       <c r="E36">
-        <v>-22.55221428730664</v>
+        <v>-27.33414704891038</v>
       </c>
       <c r="F36">
-        <v>-1.019409782317649</v>
+        <v>-2.19510335343696</v>
       </c>
       <c r="G36">
-        <v>-5.277258058640555</v>
+        <v>-6.906085944568588</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.559832343721827</v>
       </c>
       <c r="E37">
-        <v>-21.55974214306899</v>
+        <v>-27.00081861440229</v>
       </c>
       <c r="F37">
-        <v>-0.0587289110037843</v>
+        <v>-2.53156879673866</v>
       </c>
       <c r="G37">
-        <v>-3.81776045614754</v>
+        <v>-6.355701823593041</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.164897064549224</v>
       </c>
       <c r="E38">
-        <v>-21.47123305652557</v>
+        <v>-26.7449891032155</v>
       </c>
       <c r="F38">
-        <v>-0.8576843007994907</v>
+        <v>-2.399072259028282</v>
       </c>
       <c r="G38">
-        <v>-4.759617896326751</v>
+        <v>-6.28021475448559</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.7853062197673307</v>
       </c>
       <c r="E39">
-        <v>-21.91742500878587</v>
+        <v>-26.39898091453271</v>
       </c>
       <c r="F39">
-        <v>-0.9814009724075968</v>
+        <v>-2.464609374468167</v>
       </c>
       <c r="G39">
-        <v>-4.779355125435568</v>
+        <v>-5.751076872992523</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.443879781069229</v>
       </c>
       <c r="E40">
-        <v>-20.55128013523075</v>
+        <v>-25.41177504225494</v>
       </c>
       <c r="F40">
-        <v>-0.6314000057441526</v>
+        <v>-2.246781053860607</v>
       </c>
       <c r="G40">
-        <v>-3.644143330093915</v>
+        <v>-5.952498428941505</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1584129243431704</v>
       </c>
       <c r="E41">
-        <v>-19.79907126613443</v>
+        <v>-25.97790343115364</v>
       </c>
       <c r="F41">
-        <v>-0.6607523762949502</v>
+        <v>-2.215955846067632</v>
       </c>
       <c r="G41">
-        <v>-3.854289994466397</v>
+        <v>-5.602538559481133</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.05374559444262473</v>
       </c>
       <c r="E42">
-        <v>-20.12842092419333</v>
+        <v>-25.01009305576282</v>
       </c>
       <c r="F42">
-        <v>-0.7458986048939058</v>
+        <v>-2.154939131544823</v>
       </c>
       <c r="G42">
-        <v>-3.392389229172861</v>
+        <v>-5.914368504188295</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1828400674370317</v>
       </c>
       <c r="E43">
-        <v>-19.60723858825192</v>
+        <v>-23.47002415155785</v>
       </c>
       <c r="F43">
-        <v>-0.7654513890695853</v>
+        <v>-2.195638478779168</v>
       </c>
       <c r="G43">
-        <v>-4.072182738040712</v>
+        <v>-5.856676270213874</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.2225404219941768</v>
       </c>
       <c r="E44">
-        <v>-18.27289900702233</v>
+        <v>-24.12976592371819</v>
       </c>
       <c r="F44">
-        <v>-1.020033542971957</v>
+        <v>-1.962680027559474</v>
       </c>
       <c r="G44">
-        <v>-3.326094591770721</v>
+        <v>-5.232919783249678</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.1743755610827938</v>
       </c>
       <c r="E45">
-        <v>-17.95428124702678</v>
+        <v>-23.60406074064404</v>
       </c>
       <c r="F45">
-        <v>-0.9292726401168268</v>
+        <v>-1.999091745116929</v>
       </c>
       <c r="G45">
-        <v>-3.998549297592953</v>
+        <v>-5.297815061550981</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.04412890439358667</v>
       </c>
       <c r="E46">
-        <v>-18.15821222949852</v>
+        <v>-23.1750589300572</v>
       </c>
       <c r="F46">
-        <v>-0.5900222256069144</v>
+        <v>-1.901660827934457</v>
       </c>
       <c r="G46">
-        <v>-3.828386186633371</v>
+        <v>-4.991747030156406</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.1566113258013311</v>
       </c>
       <c r="E47">
-        <v>-16.31007472206306</v>
+        <v>-21.99145184743962</v>
       </c>
       <c r="F47">
-        <v>-1.073188222474796</v>
+        <v>-1.918219892316419</v>
       </c>
       <c r="G47">
-        <v>-3.66176585608393</v>
+        <v>-5.351066418975919</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4137639431057608</v>
       </c>
       <c r="E48">
-        <v>-17.34317773269151</v>
+        <v>-22.55705277850007</v>
       </c>
       <c r="F48">
-        <v>-1.030520674291399</v>
+        <v>-1.978170497991825</v>
       </c>
       <c r="G48">
-        <v>-3.473413687558062</v>
+        <v>-5.434980971623482</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7105254552550393</v>
       </c>
       <c r="E49">
-        <v>-16.5877584312411</v>
+        <v>-21.19217463439901</v>
       </c>
       <c r="F49">
-        <v>-0.5160481881695158</v>
+        <v>-1.606288206383432</v>
       </c>
       <c r="G49">
-        <v>-3.653322708076269</v>
+        <v>-5.697689756848848</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.028189807638466</v>
       </c>
       <c r="E50">
-        <v>-15.69406211194184</v>
+        <v>-20.86706955831409</v>
       </c>
       <c r="F50">
-        <v>-1.161063921665976</v>
+        <v>-2.008547559019886</v>
       </c>
       <c r="G50">
-        <v>-3.396005110431553</v>
+        <v>-5.774014874970045</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.349223398727927</v>
       </c>
       <c r="E51">
-        <v>-14.40430725428429</v>
+        <v>-20.53094601258439</v>
       </c>
       <c r="F51">
-        <v>-1.007802698269623</v>
+        <v>-2.073886694650502</v>
       </c>
       <c r="G51">
-        <v>-3.3699916513257</v>
+        <v>-5.599055826196587</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.654653653366859</v>
       </c>
       <c r="E52">
-        <v>-15.45349980558512</v>
+        <v>-20.36172341715425</v>
       </c>
       <c r="F52">
-        <v>-0.8385183642009185</v>
+        <v>-2.112309688261955</v>
       </c>
       <c r="G52">
-        <v>-3.438338333976455</v>
+        <v>-5.386804901683669</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.930765466450311</v>
       </c>
       <c r="E53">
-        <v>-14.86926756852149</v>
+        <v>-19.07722652503393</v>
       </c>
       <c r="F53">
-        <v>-0.8764095459397735</v>
+        <v>-2.040735431190466</v>
       </c>
       <c r="G53">
-        <v>-3.423772989902634</v>
+        <v>-5.879191331567634</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.163523470718852</v>
       </c>
       <c r="E54">
-        <v>-14.15968726046321</v>
+        <v>-20.4767839836973</v>
       </c>
       <c r="F54">
-        <v>-0.3235124094716323</v>
+        <v>-1.954807223763268</v>
       </c>
       <c r="G54">
-        <v>-3.662428985210072</v>
+        <v>-6.050150719627506</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.346068529928019</v>
       </c>
       <c r="E55">
-        <v>-14.01220257310723</v>
+        <v>-19.03569856499697</v>
       </c>
       <c r="F55">
-        <v>-1.19451339739102</v>
+        <v>-1.972254298001031</v>
       </c>
       <c r="G55">
-        <v>-3.756353132619964</v>
+        <v>-5.888475139333633</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.473184795880711</v>
       </c>
       <c r="E56">
-        <v>-14.84009956538722</v>
+        <v>-18.74301760972497</v>
       </c>
       <c r="F56">
-        <v>-1.403733323948688</v>
+        <v>-1.745158202890949</v>
       </c>
       <c r="G56">
-        <v>-4.10587700773362</v>
+        <v>-6.603124699237438</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.543915640892877</v>
       </c>
       <c r="E57">
-        <v>-13.19774537267437</v>
+        <v>-17.8078016368114</v>
       </c>
       <c r="F57">
-        <v>-0.882567629212185</v>
+        <v>-1.967366101957111</v>
       </c>
       <c r="G57">
-        <v>-4.503049582379684</v>
+        <v>-6.188627223484746</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.561933945593388</v>
       </c>
       <c r="E58">
-        <v>-13.58551410122832</v>
+        <v>-17.21148770800385</v>
       </c>
       <c r="F58">
-        <v>-0.9266781934112587</v>
+        <v>-1.841802999408165</v>
       </c>
       <c r="G58">
-        <v>-4.926081582200725</v>
+        <v>-6.760333295535915</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.532882725175914</v>
       </c>
       <c r="E59">
-        <v>-13.15084315718309</v>
+        <v>-17.41094983509007</v>
       </c>
       <c r="F59">
-        <v>-1.308660768761986</v>
+        <v>-1.818892013781536</v>
       </c>
       <c r="G59">
-        <v>-4.251047460722474</v>
+        <v>-5.890106854703079</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.467338585818215</v>
       </c>
       <c r="E60">
-        <v>-12.41328266442943</v>
+        <v>-17.09192506038469</v>
       </c>
       <c r="F60">
-        <v>-0.5138795223089867</v>
+        <v>-1.859626152446799</v>
       </c>
       <c r="G60">
-        <v>-4.823714286783173</v>
+        <v>-6.769810298401657</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.375940101332582</v>
       </c>
       <c r="E61">
-        <v>-12.03663623580338</v>
+        <v>-15.86161096320808</v>
       </c>
       <c r="F61">
-        <v>-1.216769972769437</v>
+        <v>-1.898614092626961</v>
       </c>
       <c r="G61">
-        <v>-4.594313381051231</v>
+        <v>-6.872537876572782</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.270635041582987</v>
       </c>
       <c r="E62">
-        <v>-11.79383950175391</v>
+        <v>-15.66526374461548</v>
       </c>
       <c r="F62">
-        <v>-0.6326889454229085</v>
+        <v>-2.067930733024374</v>
       </c>
       <c r="G62">
-        <v>-4.910111657536885</v>
+        <v>-7.200836398160686</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.16326555352572</v>
       </c>
       <c r="E63">
-        <v>-11.24366359755387</v>
+        <v>-15.32534001052357</v>
       </c>
       <c r="F63">
-        <v>-1.322987382993404</v>
+        <v>-1.655600917872087</v>
       </c>
       <c r="G63">
-        <v>-4.721474917850585</v>
+        <v>-7.403062063443731</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.063462958667871</v>
       </c>
       <c r="E64">
-        <v>-11.61892700680875</v>
+        <v>-15.01791515504843</v>
       </c>
       <c r="F64">
-        <v>-1.211430316490992</v>
+        <v>-1.996107965732046</v>
       </c>
       <c r="G64">
-        <v>-5.330123025866008</v>
+        <v>-7.238564268246865</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.980401719358948</v>
       </c>
       <c r="E65">
-        <v>-11.35660187310993</v>
+        <v>-14.76503442390227</v>
       </c>
       <c r="F65">
-        <v>-0.8791663526562903</v>
+        <v>-1.993268322275249</v>
       </c>
       <c r="G65">
-        <v>-5.315317493289805</v>
+        <v>-7.157584192519713</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.919266814851209</v>
       </c>
       <c r="E66">
-        <v>-10.40041218300598</v>
+        <v>-15.4062736396105</v>
       </c>
       <c r="F66">
-        <v>-0.9572432938397548</v>
+        <v>-2.198140148335623</v>
       </c>
       <c r="G66">
-        <v>-4.384623596982194</v>
+        <v>-7.260523241002718</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.881533471324539</v>
       </c>
       <c r="E67">
-        <v>-10.33171391448199</v>
+        <v>-14.10041678164658</v>
       </c>
       <c r="F67">
-        <v>-1.072225659552743</v>
+        <v>-2.456724973528322</v>
       </c>
       <c r="G67">
-        <v>-5.173394806572295</v>
+        <v>-7.210545757295037</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.866940999120136</v>
       </c>
       <c r="E68">
-        <v>-11.35270616088724</v>
+        <v>-15.10397800012153</v>
       </c>
       <c r="F68">
-        <v>-0.7723318087172381</v>
+        <v>-2.239240425392923</v>
       </c>
       <c r="G68">
-        <v>-5.505042913470598</v>
+        <v>-7.571927634341529</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.869525198938867</v>
       </c>
       <c r="E69">
-        <v>-9.102454732981892</v>
+        <v>-14.32821626960211</v>
       </c>
       <c r="F69">
-        <v>-1.299669668972</v>
+        <v>-2.308379282300181</v>
       </c>
       <c r="G69">
-        <v>-5.483666136758563</v>
+        <v>-7.407367181274476</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.882623973435844</v>
       </c>
       <c r="E70">
-        <v>-10.18220245999949</v>
+        <v>-15.08668818137627</v>
       </c>
       <c r="F70">
-        <v>-1.530599448422238</v>
+        <v>-2.237632564264089</v>
       </c>
       <c r="G70">
-        <v>-4.931407501166596</v>
+        <v>-6.965644860925655</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.895796594423773</v>
       </c>
       <c r="E71">
-        <v>-10.19993251914518</v>
+        <v>-14.95816290371812</v>
       </c>
       <c r="F71">
-        <v>-1.858462296245866</v>
+        <v>-2.669125002545337</v>
       </c>
       <c r="G71">
-        <v>-5.204538378799686</v>
+        <v>-7.192197444308693</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.898766591288221</v>
       </c>
       <c r="E72">
-        <v>-11.76912374115985</v>
+        <v>-14.55419249778603</v>
       </c>
       <c r="F72">
-        <v>-1.743828673209456</v>
+        <v>-2.792147502269898</v>
       </c>
       <c r="G72">
-        <v>-4.907876860166892</v>
+        <v>-7.154594889962888</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.882685432561441</v>
       </c>
       <c r="E73">
-        <v>-10.84998069607337</v>
+        <v>-14.93382923856595</v>
       </c>
       <c r="F73">
-        <v>-2.369884733590641</v>
+        <v>-2.581828332168715</v>
       </c>
       <c r="G73">
-        <v>-4.673993305972009</v>
+        <v>-6.912074992660601</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.838460172521205</v>
       </c>
       <c r="E74">
-        <v>-11.16122235275602</v>
+        <v>-14.83550196045064</v>
       </c>
       <c r="F74">
-        <v>-1.244573296277</v>
+        <v>-2.53011004174233</v>
       </c>
       <c r="G74">
-        <v>-4.852145295380397</v>
+        <v>-7.004576284268336</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.762278384537224</v>
       </c>
       <c r="E75">
-        <v>-12.64676789868865</v>
+        <v>-14.9454789963321</v>
       </c>
       <c r="F75">
-        <v>-1.887309362680956</v>
+        <v>-2.742110797671196</v>
       </c>
       <c r="G75">
-        <v>-4.175928506602371</v>
+        <v>-7.052483447515265</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.650029168039034</v>
       </c>
       <c r="E76">
-        <v>-12.52110418363331</v>
+        <v>-14.76954896461236</v>
       </c>
       <c r="F76">
-        <v>-1.629229013236561</v>
+        <v>-2.827387908319794</v>
       </c>
       <c r="G76">
-        <v>-5.111661139970831</v>
+        <v>-6.806859374894145</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.502847321801101</v>
       </c>
       <c r="E77">
-        <v>-11.07952453278532</v>
+        <v>-14.65137764278701</v>
       </c>
       <c r="F77">
-        <v>-2.19669547558514</v>
+        <v>-3.066506099546705</v>
       </c>
       <c r="G77">
-        <v>-4.189634915705716</v>
+        <v>-6.670836970952552</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.32454680871841</v>
       </c>
       <c r="E78">
-        <v>-12.84488438530562</v>
+        <v>-15.92077761174158</v>
       </c>
       <c r="F78">
-        <v>-2.4770763038803</v>
+        <v>-3.118911934917413</v>
       </c>
       <c r="G78">
-        <v>-4.030867704886344</v>
+        <v>-6.208145150047908</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.121226092488843</v>
       </c>
       <c r="E79">
-        <v>-12.06719556473147</v>
+        <v>-15.73713506659164</v>
       </c>
       <c r="F79">
-        <v>-1.888169208045062</v>
+        <v>-3.449912638462845</v>
       </c>
       <c r="G79">
-        <v>-3.580326289308742</v>
+        <v>-5.827535139087867</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.9038460660915839</v>
       </c>
       <c r="E80">
-        <v>-12.79028626922942</v>
+        <v>-16.20973313645521</v>
       </c>
       <c r="F80">
-        <v>-2.028324002394321</v>
+        <v>-3.307310846805716</v>
       </c>
       <c r="G80">
-        <v>-3.03274610802405</v>
+        <v>-5.975245846563874</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.6825258784436203</v>
       </c>
       <c r="E81">
-        <v>-13.9505896831034</v>
+        <v>-16.98551978624258</v>
       </c>
       <c r="F81">
-        <v>-2.08974330347489</v>
+        <v>-3.900511370889664</v>
       </c>
       <c r="G81">
-        <v>-3.298300604853729</v>
+        <v>-5.64136555304017</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4704552277056264</v>
       </c>
       <c r="E82">
-        <v>-14.904345591371</v>
+        <v>-17.6740474660953</v>
       </c>
       <c r="F82">
-        <v>-2.863794655672832</v>
+        <v>-3.988526235804514</v>
       </c>
       <c r="G82">
-        <v>-3.223244308603813</v>
+        <v>-5.499354101006563</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.2781867194502008</v>
       </c>
       <c r="E83">
-        <v>-15.06433975123737</v>
+        <v>-18.2749839191074</v>
       </c>
       <c r="F83">
-        <v>-2.616773839423214</v>
+        <v>-3.682918306624499</v>
       </c>
       <c r="G83">
-        <v>-3.142718502435515</v>
+        <v>-4.954674456962598</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.1172467864453553</v>
       </c>
       <c r="E84">
-        <v>-17.62140135934178</v>
+        <v>-18.99340226086491</v>
       </c>
       <c r="F84">
-        <v>-2.971398752929086</v>
+        <v>-3.810608656663834</v>
       </c>
       <c r="G84">
-        <v>-3.247746146591412</v>
+        <v>-4.776600789891943</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.003371394653864309</v>
       </c>
       <c r="E85">
-        <v>-18.44515759993092</v>
+        <v>-19.81854152082522</v>
       </c>
       <c r="F85">
-        <v>-2.749938041260249</v>
+        <v>-3.927542655977818</v>
       </c>
       <c r="G85">
-        <v>-2.949249274511065</v>
+        <v>-4.919069122228995</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.07440939718533116</v>
       </c>
       <c r="E86">
-        <v>-19.24017777136357</v>
+        <v>-20.9726732626705</v>
       </c>
       <c r="F86">
-        <v>-3.070766393099303</v>
+        <v>-3.904446116052962</v>
       </c>
       <c r="G86">
-        <v>-3.064111593541685</v>
+        <v>-4.621128338746556</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.08951123766703083</v>
       </c>
       <c r="E87">
-        <v>-20.49806919173705</v>
+        <v>-21.61620505103003</v>
       </c>
       <c r="F87">
-        <v>-3.256928713000047</v>
+        <v>-4.108214556732807</v>
       </c>
       <c r="G87">
-        <v>-2.922859868184092</v>
+        <v>-4.739898942430072</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.04141360288900545</v>
       </c>
       <c r="E88">
-        <v>-21.21378794613342</v>
+        <v>-23.15733302412283</v>
       </c>
       <c r="F88">
-        <v>-3.080078071074172</v>
+        <v>-4.421680379095779</v>
       </c>
       <c r="G88">
-        <v>-3.286755892271827</v>
+        <v>-4.545126952954656</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.07399298579642619</v>
       </c>
       <c r="E89">
-        <v>-23.37697975824772</v>
+        <v>-23.81247303813526</v>
       </c>
       <c r="F89">
-        <v>-3.868779929158026</v>
+        <v>-4.503491600531063</v>
       </c>
       <c r="G89">
-        <v>-2.430462995321762</v>
+        <v>-4.24116579244511</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2592906734693463</v>
       </c>
       <c r="E90">
-        <v>-24.6703022244333</v>
+        <v>-25.92592599142341</v>
       </c>
       <c r="F90">
-        <v>-3.594338495140939</v>
+        <v>-4.65474154787342</v>
       </c>
       <c r="G90">
-        <v>-2.364779272153943</v>
+        <v>-4.384526999432323</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5167150829129643</v>
       </c>
       <c r="E91">
-        <v>-25.35857655839521</v>
+        <v>-27.03780296124989</v>
       </c>
       <c r="F91">
-        <v>-4.094044503940518</v>
+        <v>-4.834477393463246</v>
       </c>
       <c r="G91">
-        <v>-2.717344664716245</v>
+        <v>-3.973869928973158</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.8421544076523311</v>
       </c>
       <c r="E92">
-        <v>-27.22922031799991</v>
+        <v>-29.21464845559456</v>
       </c>
       <c r="F92">
-        <v>-3.858798101954292</v>
+        <v>-5.319715137205528</v>
       </c>
       <c r="G92">
-        <v>-2.640275484386581</v>
+        <v>-4.3389094591918</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.235751075654757</v>
       </c>
       <c r="E93">
-        <v>-29.33844114894806</v>
+        <v>-30.09598481799112</v>
       </c>
       <c r="F93">
-        <v>-3.724752517200679</v>
+        <v>-5.362858168278132</v>
       </c>
       <c r="G93">
-        <v>-2.774337219140248</v>
+        <v>-4.072237563677125</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.686859251303676</v>
       </c>
       <c r="E94">
-        <v>-31.99330880714652</v>
+        <v>-33.14436509600576</v>
       </c>
       <c r="F94">
-        <v>-4.001805793638793</v>
+        <v>-5.194374037120532</v>
       </c>
       <c r="G94">
-        <v>-3.157453544907759</v>
+        <v>-4.623055068254797</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.191635377059687</v>
       </c>
       <c r="E95">
-        <v>-33.42979869751593</v>
+        <v>-34.4042417513925</v>
       </c>
       <c r="F95">
-        <v>-4.305255825734517</v>
+        <v>-5.286716293347608</v>
       </c>
       <c r="G95">
-        <v>-3.503499908226051</v>
+        <v>-4.756135163042206</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.741201968421399</v>
       </c>
       <c r="E96">
-        <v>-36.54375818234961</v>
+        <v>-36.47444316194389</v>
       </c>
       <c r="F96">
-        <v>-4.664500544245801</v>
+        <v>-5.579288204709767</v>
       </c>
       <c r="G96">
-        <v>-2.76664857631942</v>
+        <v>-4.665667641470948</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.319487949632638</v>
       </c>
       <c r="E97">
-        <v>-38.65516360245462</v>
+        <v>-38.63664235655155</v>
       </c>
       <c r="F97">
-        <v>-4.523006279806214</v>
+        <v>-5.422726765580661</v>
       </c>
       <c r="G97">
-        <v>-3.290925251383834</v>
+        <v>-5.02275745440965</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.922841522387696</v>
       </c>
       <c r="E98">
-        <v>-39.37719108485341</v>
+        <v>-40.09429493522662</v>
       </c>
       <c r="F98">
-        <v>-5.244211105175159</v>
+        <v>-6.02729580390063</v>
       </c>
       <c r="G98">
-        <v>-4.669790007180316</v>
+        <v>-5.706260831341472</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.517895030990692</v>
       </c>
       <c r="E99">
-        <v>-43.2026745806454</v>
+        <v>-42.65859351406455</v>
       </c>
       <c r="F99">
-        <v>-4.573069492161805</v>
+        <v>-5.586485889072693</v>
       </c>
       <c r="G99">
-        <v>-4.752503617315967</v>
+        <v>-6.470806941870634</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.112961732880421</v>
       </c>
       <c r="E100">
-        <v>-45.25172160931377</v>
+        <v>-45.27035706852828</v>
       </c>
       <c r="F100">
-        <v>-4.638324962684739</v>
+        <v>-5.738943596088331</v>
       </c>
       <c r="G100">
-        <v>-4.649060695126876</v>
+        <v>-6.550831485077438</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.652947306200833</v>
       </c>
       <c r="E101">
-        <v>-48.1456761455458</v>
+        <v>-47.94265160144572</v>
       </c>
       <c r="F101">
-        <v>-5.140955936783604</v>
+        <v>-5.861343991893388</v>
       </c>
       <c r="G101">
-        <v>-4.568600157573356</v>
+        <v>-7.131889244253975</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.183477391112745</v>
       </c>
       <c r="E102">
-        <v>-49.95243832346048</v>
+        <v>-50.06394374110948</v>
       </c>
       <c r="F102">
-        <v>-5.238124261499388</v>
+        <v>-5.799087211368589</v>
       </c>
       <c r="G102">
-        <v>-6.028405827928124</v>
+        <v>-7.725113073225101</v>
       </c>
     </row>
   </sheetData>
